--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T01:18:58+00:00</t>
+    <t>2024-11-07T01:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T01:51:12+00:00</t>
+    <t>2024-11-07T02:22:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T02:22:36+00:00</t>
+    <t>2024-11-07T02:46:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T02:46:23+00:00</t>
+    <t>2024-11-07T03:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T03:15:24+00:00</t>
+    <t>2024-11-07T08:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T08:39:43+00:00</t>
+    <t>2024-11-07T09:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
+++ b/jpcore-r4/feature/trial-txpackage/StructureDefinition-jp-immunization-duedateofnextdose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T09:15:05+00:00</t>
+    <t>2024-11-07T11:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
